--- a/數據類型映射表.xlsx
+++ b/數據類型映射表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Develop\Workspace\OpenSource\DevHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E4F608-44C7-4A8E-8240-7987261FED4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B713F9C-5C9E-450D-BCFB-9C604858D5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="14400" windowHeight="8182" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="17100" windowHeight="9217" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
   <si>
     <t>C++</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,14 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>int8_t</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int16_t</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int32_t</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -67,10 +59,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>short</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -79,14 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Int8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Int16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Int32</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -99,26 +79,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>byte</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sbyte</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>std::string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>String</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CHAR(m)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -131,10 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SMALLINT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>INT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -151,10 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>i16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>i32</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -187,14 +143,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NUMBER(3)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NUMBER(5)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NUMBER(10)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,22 +171,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Text</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CLOB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEXT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VARCHAR(MAX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Datetime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -263,31 +195,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>* String長度最大為4000，受Oracle限制，超過此長度需用Text</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>* Text對應MySQL和SQL Server類型最大存放2GB數據</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Char(m), m&lt;=255</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>String(m), m&lt;=4000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>* Datetime表示精確到秒的時間</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>* Number(m,n)限制條件：m&lt;=38, n&lt;=30, n&lt;=m，這是根據三個數據庫綜合得出的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>* Char長度最大為255，受MySQL限制，超過此長度無論是否定長需使用String(m)</t>
+    <t>Char(m), maxlen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Varchar(m), maxlen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>char[m * maxlen + 1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>byte[m * maxlen + 1]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -636,12 +560,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="11" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.35546875" style="1" customWidth="1"/>
@@ -669,325 +593,218 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>24</v>
+        <v>39</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="3" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/數據類型映射表.xlsx
+++ b/數據類型映射表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Develop\Workspace\OpenSource\DevHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B713F9C-5C9E-450D-BCFB-9C604858D5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99827C77-367E-4216-9936-82686A2D848B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="17100" windowHeight="9217" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="48">
   <si>
     <t>C++</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -212,6 +212,10 @@
   </si>
   <si>
     <t>byte[m * maxlen + 1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>String</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -697,7 +701,7 @@
         <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>14</v>
@@ -726,7 +730,7 @@
         <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>15</v>
